--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.##"/>
+    <numFmt numFmtId="166" formatCode="#,##0.#"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -270,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -348,10 +348,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -843,7 +839,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Em Metas, escreva cada objetivo e seus resultados-chave. Ponto de partida é o valor no dia 1; meta é onde quer chegar; valor atual é o número de hoje. Diga se maior ou menor é melhor. Exemplos do escritório: receita recorrente do consultivo, inadimplência abaixo de 10%, prazos sem atraso.</t>
+          <t>Em Metas, escreva cada objetivo e seus resultados-chave. Ponto de partida é o valor no dia 1; meta é onde quer chegar; valor atual é o número de hoje. Diga se maior ou menor é melhor. No exemplo, cada resultado-chave é um número de outra planilha do kit: inadimplência e reserva (14, 12), horas faturáveis e casos em alerta (16), propostas fechadas e paradas (15).</t>
         </is>
       </c>
     </row>
@@ -855,7 +851,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Toda sexta, atualize o valor atual (os números vêm do Painel do escritório, planilha 17) e copie para a coluna da semana em Semanas. O Painel mostra o resumo por objetivo e a lista completa com semáforo.</t>
+          <t>Toda sexta, atualize o valor atual (os números vêm dos painéis das planilhas de origem ou do Painel do escritório, 17) e copie para a coluna da semana em Semanas. O Painel mostra o resumo por objetivo e a lista completa com semáforo. No exemplo, S1 a S11 são as sextas de 03/07 a 11/09/2026.</t>
         </is>
       </c>
     </row>
@@ -879,7 +875,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Copie a tabela "Todos os resultados-chave" e use o prompt "Meta realista para o trimestre" ou "Explicar o mês" da biblioteca do kit. No fim do trimestre, o modelo de apresentação "Resultado do mês para os sócios".</t>
+          <t>Copie a tabela "Todos os resultados-chave" e use o prompt "Painel 05 · Meta realista para o trimestre" ou "Painel 06 · Meta × realizado: explicar o desvio" da biblioteca do kit. No fim do trimestre, o modelo de apresentação "Resultado do mês para os sócios".</t>
         </is>
       </c>
     </row>
@@ -915,7 +911,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Excel 2019 ou mais novo, Microsoft 365 ou Google Sheets. No celular abre nos aplicativos; para preencher, use o computador.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
@@ -981,15 +977,15 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!B4&amp;" · Metas do trimestre · "&amp;Config!B5</f>
-        <v/>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Metas do trimestre · 3º trimestre de 2026</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6">
+      <c r="A2" s="6" t="str">
         <f>"Semana "&amp;Config!B9&amp;" de 13 · "&amp;TEXT(Config!B10,"0%")&amp;" do trimestre decorrido. Nada para preencher aqui."</f>
-        <v/>
+        <v>Semana 11 de 13 · 82% do trimestre decorrido. Nada para preencher aqui.</v>
       </c>
     </row>
     <row r="4">
@@ -1021,22 +1017,22 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="15">
         <f>COUNTIFS(Metas!$B$5:$B$13,"&lt;&gt;")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16">
         <f>COUNTIFS(Metas!$J$5:$J$13,"Atingido")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
         <f>COUNTIFS(Metas!$J$5:$J$13,"Em risco")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
         <f>IFERROR(AVERAGEIFS(Metas!$H$5:$H$13,Metas!$B$5:$B$13,"&lt;&gt;"),0)</f>
-        <v/>
+        <v>0.601505376344086</v>
       </c>
       <c r="H5" s="14" t="n"/>
     </row>
@@ -1082,85 +1078,85 @@
       <c r="H8" s="22" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="23">
+      <c r="A9" s="23" t="str">
         <f>IF(Metas!$A$5="","",Metas!$A$5)</f>
-        <v/>
+        <v>Caixa mais previsível</v>
       </c>
       <c r="B9" s="24">
         <f>IF(Metas!$A$5="","",COUNTIFS(Metas!$B$5:$B$7,"&lt;&gt;"))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C9" s="25">
         <f>IF(OR(Metas!$A$5="",B9=0),"",AVERAGEIFS(Metas!$H$5:$H$7,Metas!$B$5:$B$7,"&lt;&gt;"))</f>
-        <v/>
+        <v>0.368333333333333</v>
       </c>
       <c r="D9" s="24">
         <f>IF(Metas!$A$5="","",COUNTIFS(Metas!$J$5:$J$7,"Atingido"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E9" s="24">
         <f>IF(Metas!$A$5="","",COUNTIFS(Metas!$J$5:$J$7,"Em risco"))</f>
-        <v/>
-      </c>
-      <c r="F9" s="26">
+        <v>2</v>
+      </c>
+      <c r="F9" s="26" t="str">
         <f>IF(C9="","",REPT("█",ROUND(C9*30,0)))</f>
-        <v/>
+        <v>███████████</v>
       </c>
       <c r="G9" s="21" t="n"/>
       <c r="H9" s="22" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="23">
+      <c r="A10" s="23" t="str">
         <f>IF(Metas!$A$8="","",Metas!$A$8)</f>
-        <v/>
+        <v>Horas que viram honorário</v>
       </c>
       <c r="B10" s="24">
         <f>IF(Metas!$A$8="","",COUNTIFS(Metas!$B$8:$B$10,"&lt;&gt;"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C10" s="25">
         <f>IF(OR(Metas!$A$8="",B10=0),"",AVERAGEIFS(Metas!$H$8:$H$10,Metas!$B$8:$B$10,"&lt;&gt;"))</f>
-        <v/>
+        <v>0.786854838709677</v>
       </c>
       <c r="D10" s="24">
         <f>IF(Metas!$A$8="","",COUNTIFS(Metas!$J$8:$J$10,"Atingido"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E10" s="24">
         <f>IF(Metas!$A$8="","",COUNTIFS(Metas!$J$8:$J$10,"Em risco"))</f>
-        <v/>
-      </c>
-      <c r="F10" s="26">
+        <v>0</v>
+      </c>
+      <c r="F10" s="26" t="str">
         <f>IF(C10="","",REPT("█",ROUND(C10*30,0)))</f>
-        <v/>
+        <v>████████████████████████</v>
       </c>
       <c r="G10" s="21" t="n"/>
       <c r="H10" s="22" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="23">
+      <c r="A11" s="23" t="str">
         <f>IF(Metas!$A$11="","",Metas!$A$11)</f>
-        <v/>
+        <v>Fechar mais propostas</v>
       </c>
       <c r="B11" s="24">
         <f>IF(Metas!$A$11="","",COUNTIFS(Metas!$B$11:$B$13,"&lt;&gt;"))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C11" s="25">
         <f>IF(OR(Metas!$A$11="",B11=0),"",AVERAGEIFS(Metas!$H$11:$H$13,Metas!$B$11:$B$13,"&lt;&gt;"))</f>
-        <v/>
+        <v>0.711111111111111</v>
       </c>
       <c r="D11" s="24">
         <f>IF(Metas!$A$11="","",COUNTIFS(Metas!$J$11:$J$13,"Atingido"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E11" s="24">
         <f>IF(Metas!$A$11="","",COUNTIFS(Metas!$J$11:$J$13,"Em risco"))</f>
-        <v/>
-      </c>
-      <c r="F11" s="26">
+        <v>1</v>
+      </c>
+      <c r="F11" s="26" t="str">
         <f>IF(C11="","",REPT("█",ROUND(C11*30,0)))</f>
-        <v/>
+        <v>█████████████████████</v>
       </c>
       <c r="G11" s="21" t="n"/>
       <c r="H11" s="22" t="n"/>
@@ -1215,33 +1211,33 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27">
+      <c r="A15" s="27" t="str">
         <f>IF(Metas!B5="","",Metas!B5)</f>
-        <v/>
-      </c>
-      <c r="B15" s="24">
+        <v>Inadimplência: vencido ÷ (pago + vencido) (%)</v>
+      </c>
+      <c r="B15" s="24" t="str">
         <f>IF(Metas!B5="","",Metas!C5)</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
       <c r="C15" s="28">
         <f>IF(Metas!B5="","",Metas!G5)</f>
-        <v/>
+        <v>5.1</v>
       </c>
       <c r="D15" s="28">
         <f>IF(Metas!B5="","",Metas!F5)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E15" s="25">
         <f>IF(Metas!B5="","",Metas!H5)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F15" s="25">
         <f>IF(Metas!B5="","",Metas!I5)</f>
-        <v/>
-      </c>
-      <c r="G15" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="G15" s="24" t="str">
         <f>IF(Metas!B5="","",Metas!J5)</f>
-        <v/>
+        <v>Em risco</v>
       </c>
       <c r="H15" s="26">
         <f>IF(E15="","",REPT("█",ROUND(E15*20,0)))</f>
@@ -1249,139 +1245,139 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27">
+      <c r="A16" s="27" t="str">
         <f>IF(Metas!B6="","",Metas!B6)</f>
-        <v/>
-      </c>
-      <c r="B16" s="24">
+        <v>Reserva guardada em conta separada (R$)</v>
+      </c>
+      <c r="B16" s="24" t="str">
         <f>IF(Metas!B6="","",Metas!C6)</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
       <c r="C16" s="28">
         <f>IF(Metas!B6="","",Metas!G6)</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="D16" s="28">
         <f>IF(Metas!B6="","",Metas!F6)</f>
-        <v/>
+        <v>18500</v>
       </c>
       <c r="E16" s="25">
         <f>IF(Metas!B6="","",Metas!H6)</f>
-        <v/>
+        <v>0.48</v>
       </c>
       <c r="F16" s="25">
         <f>IF(Metas!B6="","",Metas!I6)</f>
-        <v/>
-      </c>
-      <c r="G16" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="G16" s="24" t="str">
         <f>IF(Metas!B6="","",Metas!J6)</f>
-        <v/>
-      </c>
-      <c r="H16" s="26">
+        <v>Em risco</v>
+      </c>
+      <c r="H16" s="26" t="str">
         <f>IF(E16="","",REPT("█",ROUND(E16*20,0)))</f>
-        <v/>
+        <v>██████████</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27">
+      <c r="A17" s="27" t="str">
         <f>IF(Metas!B7="","",Metas!B7)</f>
-        <v/>
-      </c>
-      <c r="B17" s="24">
+        <v>Conta de provisão de impostos, 13º e férias (R$)</v>
+      </c>
+      <c r="B17" s="24" t="str">
         <f>IF(Metas!B7="","",Metas!C7)</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
       <c r="C17" s="28">
         <f>IF(Metas!B7="","",Metas!G7)</f>
-        <v/>
+        <v>9400</v>
       </c>
       <c r="D17" s="28">
         <f>IF(Metas!B7="","",Metas!F7)</f>
-        <v/>
+        <v>11320</v>
       </c>
       <c r="E17" s="25">
         <f>IF(Metas!B7="","",Metas!H7)</f>
-        <v/>
+        <v>0.625</v>
       </c>
       <c r="F17" s="25">
         <f>IF(Metas!B7="","",Metas!I7)</f>
-        <v/>
-      </c>
-      <c r="G17" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="G17" s="24" t="str">
         <f>IF(Metas!B7="","",Metas!J7)</f>
-        <v/>
-      </c>
-      <c r="H17" s="26">
+        <v>Atenção</v>
+      </c>
+      <c r="H17" s="26" t="str">
         <f>IF(E17="","",REPT("█",ROUND(E17*20,0)))</f>
-        <v/>
+        <v>█████████████</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27">
+      <c r="A18" s="27" t="str">
         <f>IF(Metas!B8="","",Metas!B8)</f>
-        <v/>
-      </c>
-      <c r="B18" s="24">
+        <v>Horas faturáveis no mês (%)</v>
+      </c>
+      <c r="B18" s="24" t="str">
         <f>IF(Metas!B8="","",Metas!C8)</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
       <c r="C18" s="28">
         <f>IF(Metas!B8="","",Metas!G8)</f>
-        <v/>
+        <v>79.5</v>
       </c>
       <c r="D18" s="28">
         <f>IF(Metas!B8="","",Metas!F8)</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="E18" s="25">
         <f>IF(Metas!B8="","",Metas!H8)</f>
-        <v/>
+        <v>0.838709677419355</v>
       </c>
       <c r="F18" s="25">
         <f>IF(Metas!B8="","",Metas!I8)</f>
-        <v/>
-      </c>
-      <c r="G18" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="G18" s="24" t="str">
         <f>IF(Metas!B8="","",Metas!J8)</f>
-        <v/>
-      </c>
-      <c r="H18" s="26">
+        <v>No ritmo</v>
+      </c>
+      <c r="H18" s="26" t="str">
         <f>IF(E18="","",REPT("█",ROUND(E18*20,0)))</f>
-        <v/>
+        <v>█████████████████</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27">
+      <c r="A19" s="27" t="str">
         <f>IF(Metas!B9="","",Metas!B9)</f>
-        <v/>
-      </c>
-      <c r="B19" s="24">
+        <v>Horas faturáveis lançadas no trimestre (h)</v>
+      </c>
+      <c r="B19" s="24" t="str">
         <f>IF(Metas!B9="","",Metas!C9)</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
       <c r="C19" s="28">
         <f>IF(Metas!B9="","",Metas!G9)</f>
-        <v/>
+        <v>514.5</v>
       </c>
       <c r="D19" s="28">
         <f>IF(Metas!B9="","",Metas!F9)</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="E19" s="25">
         <f>IF(Metas!B9="","",Metas!H9)</f>
-        <v/>
+        <v>0.735</v>
       </c>
       <c r="F19" s="25">
         <f>IF(Metas!B9="","",Metas!I9)</f>
-        <v/>
-      </c>
-      <c r="G19" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="G19" s="24" t="str">
         <f>IF(Metas!B9="","",Metas!J9)</f>
-        <v/>
-      </c>
-      <c r="H19" s="26">
+        <v>No ritmo</v>
+      </c>
+      <c r="H19" s="26" t="str">
         <f>IF(E19="","",REPT("█",ROUND(E19*20,0)))</f>
-        <v/>
+        <v>███████████████</v>
       </c>
     </row>
     <row r="20">
@@ -1419,105 +1415,105 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27">
+      <c r="A21" s="27" t="str">
         <f>IF(Metas!B11="","",Metas!B11)</f>
-        <v/>
-      </c>
-      <c r="B21" s="24">
+        <v>Propostas fechadas no trimestre</v>
+      </c>
+      <c r="B21" s="24" t="str">
         <f>IF(Metas!B11="","",Metas!C11)</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
       <c r="C21" s="28">
         <f>IF(Metas!B11="","",Metas!G11)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="D21" s="28">
         <f>IF(Metas!B11="","",Metas!F11)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="E21" s="25">
         <f>IF(Metas!B11="","",Metas!H11)</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="F21" s="25">
         <f>IF(Metas!B11="","",Metas!I11)</f>
-        <v/>
-      </c>
-      <c r="G21" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="G21" s="24" t="str">
         <f>IF(Metas!B11="","",Metas!J11)</f>
-        <v/>
-      </c>
-      <c r="H21" s="26">
+        <v>No ritmo</v>
+      </c>
+      <c r="H21" s="26" t="str">
         <f>IF(E21="","",REPT("█",ROUND(E21*20,0)))</f>
-        <v/>
+        <v>███████████████</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27">
+      <c r="A22" s="27" t="str">
         <f>IF(Metas!B12="","",Metas!B12)</f>
-        <v/>
-      </c>
-      <c r="B22" s="24">
+        <v>Honorários fechados no trimestre (R$)</v>
+      </c>
+      <c r="B22" s="24" t="str">
         <f>IF(Metas!B12="","",Metas!C12)</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
       <c r="C22" s="28">
         <f>IF(Metas!B12="","",Metas!G12)</f>
-        <v/>
+        <v>53000</v>
       </c>
       <c r="D22" s="28">
         <f>IF(Metas!B12="","",Metas!F12)</f>
-        <v/>
+        <v>60000</v>
       </c>
       <c r="E22" s="25">
         <f>IF(Metas!B12="","",Metas!H12)</f>
-        <v/>
+        <v>0.883333333333333</v>
       </c>
       <c r="F22" s="25">
         <f>IF(Metas!B12="","",Metas!I12)</f>
-        <v/>
-      </c>
-      <c r="G22" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="G22" s="24" t="str">
         <f>IF(Metas!B12="","",Metas!J12)</f>
-        <v/>
-      </c>
-      <c r="H22" s="26">
+        <v>No ritmo</v>
+      </c>
+      <c r="H22" s="26" t="str">
         <f>IF(E22="","",REPT("█",ROUND(E22*20,0)))</f>
-        <v/>
+        <v>██████████████████</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27">
+      <c r="A23" s="27" t="str">
         <f>IF(Metas!B13="","",Metas!B13)</f>
-        <v/>
-      </c>
-      <c r="B23" s="24">
+        <v>Propostas paradas há mais de 14 dias</v>
+      </c>
+      <c r="B23" s="24" t="str">
         <f>IF(Metas!B13="","",Metas!C13)</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
       <c r="C23" s="28">
         <f>IF(Metas!B13="","",Metas!G13)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D23" s="28">
         <f>IF(Metas!B13="","",Metas!F13)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E23" s="25">
         <f>IF(Metas!B13="","",Metas!H13)</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="F23" s="25">
         <f>IF(Metas!B13="","",Metas!I13)</f>
-        <v/>
-      </c>
-      <c r="G23" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="G23" s="24" t="str">
         <f>IF(Metas!B13="","",Metas!J13)</f>
-        <v/>
-      </c>
-      <c r="H23" s="26">
+        <v>Em risco</v>
+      </c>
+      <c r="H23" s="26" t="str">
         <f>IF(E23="","",REPT("█",ROUND(E23*20,0)))</f>
-        <v/>
+        <v>██████████</v>
       </c>
     </row>
     <row r="25">
@@ -1644,7 +1640,7 @@
       </c>
       <c r="B8" s="33">
         <f>TODAY()</f>
-        <v/>
+        <v>46279.0</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -1660,7 +1656,7 @@
       </c>
       <c r="B9" s="24">
         <f>IF(B8&lt;B6,0,MIN(13,INT((B8-B6)/7)+1))</f>
-        <v/>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -1671,7 +1667,7 @@
       </c>
       <c r="B10" s="25">
         <f>MAX(0,MIN(1,(B8-B6)/(B7-B6)))</f>
-        <v/>
+        <v>0.824175824175824</v>
       </c>
     </row>
     <row r="12">
@@ -1755,7 +1751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1769,7 +1765,7 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1848,64 +1844,64 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>Receita recorrente do consultivo</t>
-        </is>
-      </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Contratos de consultivo mensal ativos</t>
+          <t>Caixa mais previsível</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Inadimplência: vencido ÷ (pago + vencido) (%)</t>
         </is>
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
         <is>
-          <t>contratos</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E5" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="36" t="n">
-        <v>6</v>
-      </c>
       <c r="G5" s="36" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H5" s="25">
         <f>IF(B5="","",IF(F5=E5,"",IF(K5="Menor é melhor",MAX(0,MIN(1,(E5-G5)/(E5-F5))),MAX(0,MIN(1,(G5-E5)/(F5-E5))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I5" s="25">
         <f>IF(B5="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J5" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="J5" s="24" t="str">
         <f>IF(OR(B5="",H5=""),"",IF(H5&gt;=1,"Atingido",IF(H5&gt;=I5-0.1,"No ritmo",IF(H5&gt;=I5-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>Em risco</v>
       </c>
       <c r="K5" s="36" t="inlineStr">
         <is>
-          <t>Maior é melhor</t>
-        </is>
-      </c>
-      <c r="L5" s="37" t="inlineStr">
-        <is>
-          <t>Clínica Bem-Estar e Agência Prisma fecharam em agosto e setembro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="38" t="n"/>
-      <c r="B6" s="32" t="inlineStr">
-        <is>
-          <t>Receita recorrente mensal do consultivo (R$)</t>
+          <t>Menor é melhor</t>
+        </is>
+      </c>
+      <c r="L5" s="35" t="inlineStr">
+        <is>
+          <t>Painel da planilha 14. Piorou com Bistrô 42, Agência Prisma e Patrícia Gomes: cobrar primeiro (régua).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="37" t="n"/>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Reserva guardada em conta separada (R$)</t>
         </is>
       </c>
       <c r="C6" s="36" t="inlineStr">
@@ -1919,91 +1915,95 @@
         </is>
       </c>
       <c r="E6" s="36" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>9000</v>
+        <v>18500</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>7200</v>
+        <v>12000</v>
       </c>
       <c r="H6" s="25">
         <f>IF(B6="","",IF(F6=E6,"",IF(K6="Menor é melhor",MAX(0,MIN(1,(E6-G6)/(E6-F6))),MAX(0,MIN(1,(G6-E6)/(F6-E6))))))</f>
-        <v/>
+        <v>0.48</v>
       </c>
       <c r="I6" s="25">
         <f>IF(B6="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J6" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="J6" s="24" t="str">
         <f>IF(OR(B6="",H6=""),"",IF(H6&gt;=1,"Atingido",IF(H6&gt;=I6-0.1,"No ritmo",IF(H6&gt;=I6-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>Em risco</v>
       </c>
       <c r="K6" s="36" t="inlineStr">
         <is>
           <t>Maior é melhor</t>
         </is>
       </c>
-      <c r="L6" s="37" t="inlineStr">
-        <is>
-          <t>Mesmo valor da linha "Consultivo mensal" da planilha 18.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="39" t="n"/>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>Propostas de consultivo enviadas no trimestre</t>
+      <c r="L6" s="35" t="inlineStr">
+        <is>
+          <t>Meta = 1 mês de custo fixo com pró-labore (planilha 12). Aporte de R$ 3.000 no fechamento de cada mês.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="38" t="n"/>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Conta de provisão de impostos, 13º e férias (R$)</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
         <is>
-          <t>propostas</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>12</v>
+        <v>11320</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>10</v>
+        <v>9400</v>
       </c>
       <c r="H7" s="25">
         <f>IF(B7="","",IF(F7=E7,"",IF(K7="Menor é melhor",MAX(0,MIN(1,(E7-G7)/(E7-F7))),MAX(0,MIN(1,(G7-E7)/(F7-E7))))))</f>
-        <v/>
+        <v>0.625</v>
       </c>
       <c r="I7" s="25">
         <f>IF(B7="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J7" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="J7" s="24" t="str">
         <f>IF(OR(B7="",H7=""),"",IF(H7&gt;=1,"Atingido",IF(H7&gt;=I7-0.1,"No ritmo",IF(H7&gt;=I7-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>Atenção</v>
       </c>
       <c r="K7" s="36" t="inlineStr">
         <is>
           <t>Maior é melhor</t>
         </is>
       </c>
-      <c r="L7" s="37" t="inlineStr"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
+      <c r="L7" s="35" t="inlineStr">
+        <is>
+          <t>Meta = saldo provisionado de setembro na planilha 10; atual = o que já está na conta separada (planilha 12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>Inadimplência abaixo de 10% do a receber</t>
-        </is>
-      </c>
-      <c r="B8" s="32" t="inlineStr">
-        <is>
-          <t>Inadimplência: vencido ÷ parcelas em aberto (%)</t>
+          <t>Horas que viram honorário</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Horas faturáveis no mês (%)</t>
         </is>
       </c>
       <c r="C8" s="36" t="inlineStr">
@@ -2017,112 +2017,94 @@
         </is>
       </c>
       <c r="E8" s="36" t="n">
-        <v>18.6</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>17.4</v>
+        <v>79.5</v>
       </c>
       <c r="H8" s="25">
         <f>IF(B8="","",IF(F8=E8,"",IF(K8="Menor é melhor",MAX(0,MIN(1,(E8-G8)/(E8-F8))),MAX(0,MIN(1,(G8-E8)/(F8-E8))))))</f>
-        <v/>
+        <v>0.838709677419355</v>
       </c>
       <c r="I8" s="25">
         <f>IF(B8="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J8" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="J8" s="24" t="str">
         <f>IF(OR(B8="",H8=""),"",IF(H8&gt;=1,"Atingido",IF(H8&gt;=I8-0.1,"No ritmo",IF(H8&gt;=I8-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>No ritmo</v>
       </c>
       <c r="K8" s="36" t="inlineStr">
         <is>
-          <t>Menor é melhor</t>
-        </is>
-      </c>
-      <c r="L8" s="37" t="inlineStr">
-        <is>
-          <t>Painel da planilha 14: R$ 26.590 vencidos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="38" t="n"/>
-      <c r="B9" s="32" t="inlineStr">
-        <is>
-          <t>Parcelas vencidas</t>
+          <t>Maior é melhor</t>
+        </is>
+      </c>
+      <c r="L8" s="35" t="inlineStr">
+        <is>
+          <t>Painel da planilha 16 (mês do painel). Partida = julho fechado; atual = setembro até 11/09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="37" t="n"/>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Horas faturáveis lançadas no trimestre (h)</t>
         </is>
       </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>Júlia Prado</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="D9" s="36" t="inlineStr">
         <is>
-          <t>parcelas</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E9" s="36" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>3</v>
+        <v>700</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>8</v>
+        <v>514.5</v>
       </c>
       <c r="H9" s="25">
         <f>IF(B9="","",IF(F9=E9,"",IF(K9="Menor é melhor",MAX(0,MIN(1,(E9-G9)/(E9-F9))),MAX(0,MIN(1,(G9-E9)/(F9-E9))))))</f>
-        <v/>
+        <v>0.735</v>
       </c>
       <c r="I9" s="25">
         <f>IF(B9="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J9" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="J9" s="24" t="str">
         <f>IF(OR(B9="",H9=""),"",IF(H9&gt;=1,"Atingido",IF(H9&gt;=I9-0.1,"No ritmo",IF(H9&gt;=I9-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>No ritmo</v>
       </c>
       <c r="K9" s="36" t="inlineStr">
         <is>
-          <t>Menor é melhor</t>
-        </is>
-      </c>
-      <c r="L9" s="37" t="inlineStr">
-        <is>
-          <t>Régua de cobrança da planilha 14.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="39" t="n"/>
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>Cobranças enviadas na data da régua (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>Júlia Prado</t>
-        </is>
-      </c>
-      <c r="D10" s="36" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E10" s="36" t="n">
-        <v>40</v>
-      </c>
-      <c r="F10" s="36" t="n">
-        <v>100</v>
-      </c>
-      <c r="G10" s="36" t="n">
-        <v>90</v>
-      </c>
+          <t>Maior é melhor</t>
+        </is>
+      </c>
+      <c r="L9" s="35" t="inlineStr">
+        <is>
+          <t>Soma das horas faturáveis de julho, agosto e setembro na planilha 16 (Painel, trocando o mês em Config). Meta = 2,5 meses × 280 h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="38" t="n"/>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
       <c r="H10" s="25">
         <f>IF(B10="","",IF(F10=E10,"",IF(K10="Menor é melhor",MAX(0,MIN(1,(E10-G10)/(E10-F10))),MAX(0,MIN(1,(G10-E10)/(F10-E10))))))</f>
         <v/>
@@ -2135,22 +2117,18 @@
         <f>IF(OR(B10="",H10=""),"",IF(H10&gt;=1,"Atingido",IF(H10&gt;=I10-0.1,"No ritmo",IF(H10&gt;=I10-0.25,"Atenção","Em risco"))))</f>
         <v/>
       </c>
-      <c r="K10" s="36" t="inlineStr">
-        <is>
-          <t>Maior é melhor</t>
-        </is>
-      </c>
-      <c r="L10" s="37" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
+      <c r="K10" s="36" t="n"/>
+      <c r="L10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="44" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>Prazos sem atraso</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>Prazos atrasados na sexta-feira</t>
+          <t>Fechar mais propostas</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Propostas fechadas no trimestre</t>
         </is>
       </c>
       <c r="C11" s="36" t="inlineStr">
@@ -2160,91 +2138,95 @@
       </c>
       <c r="D11" s="36" t="inlineStr">
         <is>
-          <t>prazos</t>
+          <t>propostas</t>
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H11" s="25">
         <f>IF(B11="","",IF(F11=E11,"",IF(K11="Menor é melhor",MAX(0,MIN(1,(E11-G11)/(E11-F11))),MAX(0,MIN(1,(G11-E11)/(F11-E11))))))</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="I11" s="25">
         <f>IF(B11="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J11" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="J11" s="24" t="str">
         <f>IF(OR(B11="",H11=""),"",IF(H11&gt;=1,"Atingido",IF(H11&gt;=I11-0.1,"No ritmo",IF(H11&gt;=I11-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>No ritmo</v>
       </c>
       <c r="K11" s="36" t="inlineStr">
         <is>
-          <t>Menor é melhor</t>
-        </is>
-      </c>
-      <c r="L11" s="37" t="inlineStr">
-        <is>
-          <t>Piorou em setembro: 7 atrasados na planilha 01. Prioridade da segunda-feira.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="38" t="n"/>
-      <c r="B12" s="32" t="inlineStr">
-        <is>
-          <t>Prazos lançados na agenda no mesmo dia (%)</t>
+          <t>Maior é melhor</t>
+        </is>
+      </c>
+      <c r="L11" s="35" t="inlineStr">
+        <is>
+          <t>Painel da planilha 15 (funil). Fechadas de julho a setembro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="37" t="n"/>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Honorários fechados no trimestre (R$)</t>
         </is>
       </c>
       <c r="C12" s="36" t="inlineStr">
         <is>
-          <t>Júlia Prado</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="D12" s="36" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="E12" s="36" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>100</v>
+        <v>60000</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>85</v>
+        <v>53000</v>
       </c>
       <c r="H12" s="25">
         <f>IF(B12="","",IF(F12=E12,"",IF(K12="Menor é melhor",MAX(0,MIN(1,(E12-G12)/(E12-F12))),MAX(0,MIN(1,(G12-E12)/(F12-E12))))))</f>
-        <v/>
+        <v>0.883333333333333</v>
       </c>
       <c r="I12" s="25">
         <f>IF(B12="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J12" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="J12" s="24" t="str">
         <f>IF(OR(B12="",H12=""),"",IF(H12&gt;=1,"Atingido",IF(H12&gt;=I12-0.1,"No ritmo",IF(H12&gt;=I12-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>No ritmo</v>
       </c>
       <c r="K12" s="36" t="inlineStr">
         <is>
           <t>Maior é melhor</t>
         </is>
       </c>
-      <c r="L12" s="37" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="39" t="n"/>
-      <c r="B13" s="32" t="inlineStr">
-        <is>
-          <t>Rotinas de segunda-feira feitas (semanas)</t>
+      <c r="L12" s="35" t="inlineStr">
+        <is>
+          <t>KPI "Fechado no trimestre" da planilha 15; meta = Config da 15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="38" t="n"/>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>Propostas paradas há mais de 14 dias</t>
         </is>
       </c>
       <c r="C13" s="36" t="inlineStr">
@@ -2254,38 +2236,38 @@
       </c>
       <c r="D13" s="36" t="inlineStr">
         <is>
-          <t>semanas</t>
+          <t>propostas</t>
         </is>
       </c>
       <c r="E13" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="36" t="n">
-        <v>13</v>
-      </c>
       <c r="G13" s="36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H13" s="25">
         <f>IF(B13="","",IF(F13=E13,"",IF(K13="Menor é melhor",MAX(0,MIN(1,(E13-G13)/(E13-F13))),MAX(0,MIN(1,(G13-E13)/(F13-E13))))))</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="I13" s="25">
         <f>IF(B13="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J13" s="24">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="J13" s="24" t="str">
         <f>IF(OR(B13="",H13=""),"",IF(H13&gt;=1,"Atingido",IF(H13&gt;=I13-0.1,"No ritmo",IF(H13&gt;=I13-0.25,"Atenção","Em risco"))))</f>
-        <v/>
+        <v>Em risco</v>
       </c>
       <c r="K13" s="36" t="inlineStr">
         <is>
-          <t>Maior é melhor</t>
-        </is>
-      </c>
-      <c r="L13" s="37" t="inlineStr">
-        <is>
-          <t>Planilha 03 · Rotina da semana.</t>
+          <t>Menor é melhor</t>
+        </is>
+      </c>
+      <c r="L13" s="35" t="inlineStr">
+        <is>
+          <t>Situação "Parada" na planilha 15. Retomar contato na sexta.</t>
         </is>
       </c>
     </row>
@@ -2293,6 +2275,13 @@
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso). A planilha avisa; a ação é do escritório.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Inadimplência = vencido ÷ (pago + vencido), a mesma conta das planilhas 14, 17 e 20 (não é vencido ÷ em aberto). Valores em % digitados como 5,1 (não 0,051).</t>
         </is>
       </c>
     </row>
@@ -2451,226 +2440,226 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27">
+      <c r="A5" s="27" t="str">
         <f>IF(Metas!B5="","",Metas!B5)</f>
-        <v/>
+        <v>Inadimplência: vencido ÷ (pago + vencido) (%)</v>
       </c>
       <c r="B5" s="24">
         <f>IF(Metas!B5="","",Metas!F5)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="E5" s="36" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="F5" s="36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G5" s="36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H5" s="36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I5" s="36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J5" s="36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K5" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" s="36" t="n">
-        <v>5</v>
-      </c>
       <c r="L5" s="36" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="M5" s="36" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="N5" s="36" t="n"/>
       <c r="O5" s="36" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27">
+      <c r="A6" s="27" t="str">
         <f>IF(Metas!B6="","",Metas!B6)</f>
-        <v/>
+        <v>Reserva guardada em conta separada (R$)</v>
       </c>
       <c r="B6" s="24">
         <f>IF(Metas!B6="","",Metas!F6)</f>
-        <v/>
+        <v>18500</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="I6" s="36" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="J6" s="36" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="K6" s="36" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L6" s="36" t="n">
-        <v>7200</v>
+        <v>12000</v>
       </c>
       <c r="M6" s="36" t="n">
-        <v>7200</v>
+        <v>12000</v>
       </c>
       <c r="N6" s="36" t="n"/>
       <c r="O6" s="36" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27">
+      <c r="A7" s="27" t="str">
         <f>IF(Metas!B7="","",Metas!B7)</f>
-        <v/>
+        <v>Conta de provisão de impostos, 13º e férias (R$)</v>
       </c>
       <c r="B7" s="24">
         <f>IF(Metas!B7="","",Metas!F7)</f>
-        <v/>
+        <v>11320</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>1</v>
+        <v>6200</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>2</v>
+        <v>6200</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>3</v>
+        <v>6200</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>4</v>
+        <v>6200</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>5</v>
+        <v>7800</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>5</v>
+        <v>7800</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>6</v>
+        <v>7800</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>7</v>
+        <v>7800</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>8</v>
+        <v>7800</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>9</v>
+        <v>9400</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>10</v>
+        <v>9400</v>
       </c>
       <c r="N7" s="36" t="n"/>
       <c r="O7" s="36" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27">
+      <c r="A8" s="27" t="str">
         <f>IF(Metas!B8="","",Metas!B8)</f>
-        <v/>
+        <v>Horas faturáveis no mês (%)</v>
       </c>
       <c r="B8" s="24">
         <f>IF(Metas!B8="","",Metas!F8)</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>18.6</v>
+        <v>81.7</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>18.4</v>
+        <v>81.8</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>18.9</v>
+        <v>73.8</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>19.7</v>
+        <v>76.2</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>19.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>18.3</v>
+        <v>75.5</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>17.8</v>
+        <v>80</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>17.1</v>
+        <v>80.3</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>17.1</v>
+        <v>82.3</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>17.6</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>17.4</v>
+        <v>79.5</v>
       </c>
       <c r="N8" s="36" t="n"/>
       <c r="O8" s="36" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27">
+      <c r="A9" s="27" t="str">
         <f>IF(Metas!B9="","",Metas!B9)</f>
-        <v/>
+        <v>Horas faturáveis lançadas no trimestre (h)</v>
       </c>
       <c r="B9" s="24">
         <f>IF(Metas!B9="","",Metas!F9)</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>10</v>
+        <v>24.5</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>9</v>
+        <v>87.5</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>9</v>
+        <v>126.5</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>9</v>
+        <v>179.5</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>8</v>
+        <v>235</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>8</v>
+        <v>299.5</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>7</v>
+        <v>359</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>8</v>
+        <v>420.5</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>8</v>
+        <v>464</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>8</v>
+        <v>514.5</v>
       </c>
       <c r="N9" s="36" t="n"/>
       <c r="O9" s="36" t="n"/>
@@ -2684,173 +2673,151 @@
         <f>IF(Metas!B10="","",Metas!F10)</f>
         <v/>
       </c>
-      <c r="C10" s="36" t="n">
-        <v>40</v>
-      </c>
-      <c r="D10" s="36" t="n">
-        <v>50</v>
-      </c>
-      <c r="E10" s="36" t="n">
-        <v>50</v>
-      </c>
-      <c r="F10" s="36" t="n">
-        <v>60</v>
-      </c>
-      <c r="G10" s="36" t="n">
-        <v>60</v>
-      </c>
-      <c r="H10" s="36" t="n">
-        <v>70</v>
-      </c>
-      <c r="I10" s="36" t="n">
-        <v>70</v>
-      </c>
-      <c r="J10" s="36" t="n">
-        <v>75</v>
-      </c>
-      <c r="K10" s="36" t="n">
-        <v>80</v>
-      </c>
-      <c r="L10" s="36" t="n">
-        <v>90</v>
-      </c>
-      <c r="M10" s="36" t="n">
-        <v>90</v>
-      </c>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="36" t="n"/>
+      <c r="J10" s="36" t="n"/>
+      <c r="K10" s="36" t="n"/>
+      <c r="L10" s="36" t="n"/>
+      <c r="M10" s="36" t="n"/>
       <c r="N10" s="36" t="n"/>
       <c r="O10" s="36" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="27">
+      <c r="A11" s="27" t="str">
         <f>IF(Metas!B11="","",Metas!B11)</f>
-        <v/>
+        <v>Propostas fechadas no trimestre</v>
       </c>
       <c r="B11" s="24">
         <f>IF(Metas!B11="","",Metas!F11)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C11" s="36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H11" s="36" t="n">
         <v>4</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L11" s="36" t="n">
         <v>6</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N11" s="36" t="n"/>
       <c r="O11" s="36" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="27">
+      <c r="A12" s="27" t="str">
         <f>IF(Metas!B12="","",Metas!B12)</f>
-        <v/>
+        <v>Honorários fechados no trimestre (R$)</v>
       </c>
       <c r="B12" s="24">
         <f>IF(Metas!B12="","",Metas!F12)</f>
-        <v/>
+        <v>60000</v>
       </c>
       <c r="C12" s="36" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>65</v>
+        <v>6000</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>70</v>
+        <v>6000</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>70</v>
+        <v>21500</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>75</v>
+        <v>26900</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>80</v>
+        <v>40100</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>80</v>
+        <v>48500</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>85</v>
+        <v>53000</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>85</v>
+        <v>53000</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>85</v>
+        <v>53000</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>85</v>
+        <v>53000</v>
       </c>
       <c r="N12" s="36" t="n"/>
       <c r="O12" s="36" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27">
+      <c r="A13" s="27" t="str">
         <f>IF(Metas!B13="","",Metas!B13)</f>
-        <v/>
+        <v>Propostas paradas há mais de 14 dias</v>
       </c>
       <c r="B13" s="24">
         <f>IF(Metas!B13="","",Metas!F13)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C13" s="36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="36" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="I13" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="36" t="n">
-        <v>9</v>
-      </c>
       <c r="M13" s="36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N13" s="36" t="n"/>
       <c r="O13" s="36" t="n"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -935,17 +935,29 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1221,7 +1233,7 @@
       </c>
       <c r="C15" s="28">
         <f>IF(Metas!B5="","",Metas!G5)</f>
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="D15" s="28">
         <f>IF(Metas!B5="","",Metas!F5)</f>
@@ -1638,9 +1650,8 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B8" s="33">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B8" s="33" t="n">
+        <v>46279</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -1866,13 +1877,13 @@
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="F5" s="36" t="n">
         <v>3</v>
       </c>
       <c r="G5" s="36" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="H5" s="25">
         <f>IF(B5="","",IF(F5=E5,"",IF(K5="Menor é melhor",MAX(0,MIN(1,(E5-G5)/(E5-F5))),MAX(0,MIN(1,(G5-E5)/(F5-E5))))))</f>
@@ -2316,7 +2327,7 @@
     <dataValidation sqref="C5:C13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$B$13,0,0,MAX(1,COUNTA(Config!$B$13:$B$24)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:G13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal"/>
+    <dataValidation sqref="E5:G13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2449,37 +2460,37 @@
         <v>3</v>
       </c>
       <c r="C5" s="36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E5" s="36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F5" s="36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G5" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J5" s="36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K5" s="36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L5" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="36" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E5" s="36" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F5" s="36" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G5" s="36" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H5" s="36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I5" s="36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J5" s="36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K5" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" s="36" t="n">
-        <v>4.5</v>
-      </c>
       <c r="M5" s="36" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="N5" s="36" t="n"/>
       <c r="O5" s="36" t="n"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
@@ -827,7 +827,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Em Config, preencha o trimestre, as datas de início e fim, deixe a data de referência em =HOJE() e liste as pessoas do escritório (de cima para baixo, sem pular linha).</t>
+          <t>Em Config, preencha o trimestre, as datas de início e fim, troque a data de referência por =HOJE() (no exemplo ela está congelada em 14/09/2026) e liste as pessoas do escritório (de cima para baixo, sem pular linha).</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
@@ -923,7 +923,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
   </mergeCells>
   <conditionalFormatting sqref="C4:O4">
     <cfRule type="expression" priority="1" dxfId="4">
-      <formula>COLUMN()-2=Config!$B$9</formula>
+      <formula>COLUMN()-2=INDIRECT("Config!$B$9")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
@@ -1886,7 +1886,7 @@
         <v>4.6</v>
       </c>
       <c r="H5" s="25">
-        <f>IF(B5="","",IF(F5=E5,"",IF(K5="Menor é melhor",MAX(0,MIN(1,(E5-G5)/(E5-F5))),MAX(0,MIN(1,(G5-E5)/(F5-E5))))))</f>
+        <f>IF(OR(B5="",G5=""),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),IF(G5=0,0,MAX(0,F5/G5)))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),IF(F5=0,0,MAX(0,G5/F5))))))</f>
         <v>0</v>
       </c>
       <c r="I5" s="25">
@@ -1935,7 +1935,7 @@
         <v>12000</v>
       </c>
       <c r="H6" s="25">
-        <f>IF(B6="","",IF(F6=E6,"",IF(K6="Menor é melhor",MAX(0,MIN(1,(E6-G6)/(E6-F6))),MAX(0,MIN(1,(G6-E6)/(F6-E6))))))</f>
+        <f>IF(OR(B6="",G6=""),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),IF(G6=0,0,MAX(0,F6/G6)))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),IF(F6=0,0,MAX(0,G6/F6))))))</f>
         <v>0.48</v>
       </c>
       <c r="I6" s="25">
@@ -1984,7 +1984,7 @@
         <v>9400</v>
       </c>
       <c r="H7" s="25">
-        <f>IF(B7="","",IF(F7=E7,"",IF(K7="Menor é melhor",MAX(0,MIN(1,(E7-G7)/(E7-F7))),MAX(0,MIN(1,(G7-E7)/(F7-E7))))))</f>
+        <f>IF(OR(B7="",G7=""),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),IF(G7=0,0,MAX(0,F7/G7)))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),IF(F7=0,0,MAX(0,G7/F7))))))</f>
         <v>0.625</v>
       </c>
       <c r="I7" s="25">
@@ -2037,7 +2037,7 @@
         <v>79.5</v>
       </c>
       <c r="H8" s="25">
-        <f>IF(B8="","",IF(F8=E8,"",IF(K8="Menor é melhor",MAX(0,MIN(1,(E8-G8)/(E8-F8))),MAX(0,MIN(1,(G8-E8)/(F8-E8))))))</f>
+        <f>IF(OR(B8="",G8=""),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),IF(G8=0,0,MAX(0,F8/G8)))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),IF(F8=0,0,MAX(0,G8/F8))))))</f>
         <v>0.838709677419355</v>
       </c>
       <c r="I8" s="25">
@@ -2086,7 +2086,7 @@
         <v>514.5</v>
       </c>
       <c r="H9" s="25">
-        <f>IF(B9="","",IF(F9=E9,"",IF(K9="Menor é melhor",MAX(0,MIN(1,(E9-G9)/(E9-F9))),MAX(0,MIN(1,(G9-E9)/(F9-E9))))))</f>
+        <f>IF(OR(B9="",G9=""),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),IF(G9=0,0,MAX(0,F9/G9)))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),IF(F9=0,0,MAX(0,G9/F9))))))</f>
         <v>0.735</v>
       </c>
       <c r="I9" s="25">
@@ -2117,7 +2117,7 @@
       <c r="F10" s="36" t="n"/>
       <c r="G10" s="36" t="n"/>
       <c r="H10" s="25">
-        <f>IF(B10="","",IF(F10=E10,"",IF(K10="Menor é melhor",MAX(0,MIN(1,(E10-G10)/(E10-F10))),MAX(0,MIN(1,(G10-E10)/(F10-E10))))))</f>
+        <f>IF(OR(B10="",G10=""),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),IF(G10=0,0,MAX(0,F10/G10)))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),IF(F10=0,0,MAX(0,G10/F10))))))</f>
         <v/>
       </c>
       <c r="I10" s="25">
@@ -2162,7 +2162,7 @@
         <v>6</v>
       </c>
       <c r="H11" s="25">
-        <f>IF(B11="","",IF(F11=E11,"",IF(K11="Menor é melhor",MAX(0,MIN(1,(E11-G11)/(E11-F11))),MAX(0,MIN(1,(G11-E11)/(F11-E11))))))</f>
+        <f>IF(OR(B11="",G11=""),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),IF(G11=0,0,MAX(0,F11/G11)))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),IF(F11=0,0,MAX(0,G11/F11))))))</f>
         <v>0.75</v>
       </c>
       <c r="I11" s="25">
@@ -2211,7 +2211,7 @@
         <v>53000</v>
       </c>
       <c r="H12" s="25">
-        <f>IF(B12="","",IF(F12=E12,"",IF(K12="Menor é melhor",MAX(0,MIN(1,(E12-G12)/(E12-F12))),MAX(0,MIN(1,(G12-E12)/(F12-E12))))))</f>
+        <f>IF(OR(B12="",G12=""),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),IF(G12=0,0,MAX(0,F12/G12)))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),IF(F12=0,0,MAX(0,G12/F12))))))</f>
         <v>0.883333333333333</v>
       </c>
       <c r="I12" s="25">
@@ -2260,7 +2260,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="25">
-        <f>IF(B13="","",IF(F13=E13,"",IF(K13="Menor é melhor",MAX(0,MIN(1,(E13-G13)/(E13-F13))),MAX(0,MIN(1,(G13-E13)/(F13-E13))))))</f>
+        <f>IF(OR(B13="",G13=""),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),IF(G13=0,0,MAX(0,F13/G13)))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),IF(F13=0,0,MAX(0,G13/F13))))))</f>
         <v>0.5</v>
       </c>
       <c r="I13" s="25">
@@ -2285,7 +2285,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso). A planilha avisa; a ação é do escritório.</t>
+          <t>Progresso: valor atual no alvo = 100 %; fora do alvo, é o caminho andado entre o ponto de partida e a meta — e, quando o ponto de partida já estava dentro da meta (um teto ou piso a manter), é meta ÷ atual (16 pacientes para um teto de 8 = 50 %). Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso). A planilha avisa; a ação é do escritório.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
@@ -360,7 +360,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <color rgb="008A86A0"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00EDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1556,15 +1568,18 @@
   </mergeCells>
   <conditionalFormatting sqref="G15:G23">
     <cfRule type="expression" priority="1" dxfId="0">
+      <formula>G15="Faltam dados"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>G15="Atingido"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>G15="No ritmo"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="4" dxfId="3">
       <formula>G15="Atenção"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="5" dxfId="4">
       <formula>G15="Em risco"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1886,7 +1901,7 @@
         <v>4.6</v>
       </c>
       <c r="H5" s="25">
-        <f>IF(OR(B5="",G5=""),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),IF(G5=0,0,MAX(0,F5/G5)))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),IF(F5=0,0,MAX(0,G5/F5))))))</f>
+        <f>IF(B5="","",IF(OR(NOT(ISNUMBER(E5)),NOT(ISNUMBER(F5)),NOT(ISNUMBER(G5))),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),MAX(0,1-(G5-F5)/MAX(ABS(F5),ABS(G5))))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),MAX(0,1-(F5-G5)/MAX(ABS(F5),ABS(G5))))))))</f>
         <v>0</v>
       </c>
       <c r="I5" s="25">
@@ -1894,7 +1909,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J5" s="24" t="str">
-        <f>IF(OR(B5="",H5=""),"",IF(H5&gt;=1,"Atingido",IF(H5&gt;=I5-0.1,"No ritmo",IF(H5&gt;=I5-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B5="","",IF(H5="","Faltam dados",IF(H5&gt;=1,"Atingido",IF(H5&gt;=I5-0.1,"No ritmo",IF(H5&gt;=I5-0.25,"Atenção","Em risco")))))</f>
         <v>Em risco</v>
       </c>
       <c r="K5" s="36" t="inlineStr">
@@ -1935,7 +1950,7 @@
         <v>12000</v>
       </c>
       <c r="H6" s="25">
-        <f>IF(OR(B6="",G6=""),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),IF(G6=0,0,MAX(0,F6/G6)))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),IF(F6=0,0,MAX(0,G6/F6))))))</f>
+        <f>IF(B6="","",IF(OR(NOT(ISNUMBER(E6)),NOT(ISNUMBER(F6)),NOT(ISNUMBER(G6))),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),MAX(0,1-(G6-F6)/MAX(ABS(F6),ABS(G6))))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),MAX(0,1-(F6-G6)/MAX(ABS(F6),ABS(G6))))))))</f>
         <v>0.48</v>
       </c>
       <c r="I6" s="25">
@@ -1943,7 +1958,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J6" s="24" t="str">
-        <f>IF(OR(B6="",H6=""),"",IF(H6&gt;=1,"Atingido",IF(H6&gt;=I6-0.1,"No ritmo",IF(H6&gt;=I6-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B6="","",IF(H6="","Faltam dados",IF(H6&gt;=1,"Atingido",IF(H6&gt;=I6-0.1,"No ritmo",IF(H6&gt;=I6-0.25,"Atenção","Em risco")))))</f>
         <v>Em risco</v>
       </c>
       <c r="K6" s="36" t="inlineStr">
@@ -1984,7 +1999,7 @@
         <v>9400</v>
       </c>
       <c r="H7" s="25">
-        <f>IF(OR(B7="",G7=""),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),IF(G7=0,0,MAX(0,F7/G7)))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),IF(F7=0,0,MAX(0,G7/F7))))))</f>
+        <f>IF(B7="","",IF(OR(NOT(ISNUMBER(E7)),NOT(ISNUMBER(F7)),NOT(ISNUMBER(G7))),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),MAX(0,1-(G7-F7)/MAX(ABS(F7),ABS(G7))))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),MAX(0,1-(F7-G7)/MAX(ABS(F7),ABS(G7))))))))</f>
         <v>0.625</v>
       </c>
       <c r="I7" s="25">
@@ -1992,7 +2007,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J7" s="24" t="str">
-        <f>IF(OR(B7="",H7=""),"",IF(H7&gt;=1,"Atingido",IF(H7&gt;=I7-0.1,"No ritmo",IF(H7&gt;=I7-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B7="","",IF(H7="","Faltam dados",IF(H7&gt;=1,"Atingido",IF(H7&gt;=I7-0.1,"No ritmo",IF(H7&gt;=I7-0.25,"Atenção","Em risco")))))</f>
         <v>Atenção</v>
       </c>
       <c r="K7" s="36" t="inlineStr">
@@ -2037,7 +2052,7 @@
         <v>79.5</v>
       </c>
       <c r="H8" s="25">
-        <f>IF(OR(B8="",G8=""),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),IF(G8=0,0,MAX(0,F8/G8)))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),IF(F8=0,0,MAX(0,G8/F8))))))</f>
+        <f>IF(B8="","",IF(OR(NOT(ISNUMBER(E8)),NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),MAX(0,1-(G8-F8)/MAX(ABS(F8),ABS(G8))))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),MAX(0,1-(F8-G8)/MAX(ABS(F8),ABS(G8))))))))</f>
         <v>0.838709677419355</v>
       </c>
       <c r="I8" s="25">
@@ -2045,7 +2060,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J8" s="24" t="str">
-        <f>IF(OR(B8="",H8=""),"",IF(H8&gt;=1,"Atingido",IF(H8&gt;=I8-0.1,"No ritmo",IF(H8&gt;=I8-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B8="","",IF(H8="","Faltam dados",IF(H8&gt;=1,"Atingido",IF(H8&gt;=I8-0.1,"No ritmo",IF(H8&gt;=I8-0.25,"Atenção","Em risco")))))</f>
         <v>No ritmo</v>
       </c>
       <c r="K8" s="36" t="inlineStr">
@@ -2086,7 +2101,7 @@
         <v>514.5</v>
       </c>
       <c r="H9" s="25">
-        <f>IF(OR(B9="",G9=""),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),IF(G9=0,0,MAX(0,F9/G9)))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),IF(F9=0,0,MAX(0,G9/F9))))))</f>
+        <f>IF(B9="","",IF(OR(NOT(ISNUMBER(E9)),NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),MAX(0,1-(G9-F9)/MAX(ABS(F9),ABS(G9))))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),MAX(0,1-(F9-G9)/MAX(ABS(F9),ABS(G9))))))))</f>
         <v>0.735</v>
       </c>
       <c r="I9" s="25">
@@ -2094,7 +2109,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J9" s="24" t="str">
-        <f>IF(OR(B9="",H9=""),"",IF(H9&gt;=1,"Atingido",IF(H9&gt;=I9-0.1,"No ritmo",IF(H9&gt;=I9-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B9="","",IF(H9="","Faltam dados",IF(H9&gt;=1,"Atingido",IF(H9&gt;=I9-0.1,"No ritmo",IF(H9&gt;=I9-0.25,"Atenção","Em risco")))))</f>
         <v>No ritmo</v>
       </c>
       <c r="K9" s="36" t="inlineStr">
@@ -2117,7 +2132,7 @@
       <c r="F10" s="36" t="n"/>
       <c r="G10" s="36" t="n"/>
       <c r="H10" s="25">
-        <f>IF(OR(B10="",G10=""),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),IF(G10=0,0,MAX(0,F10/G10)))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),IF(F10=0,0,MAX(0,G10/F10))))))</f>
+        <f>IF(B10="","",IF(OR(NOT(ISNUMBER(E10)),NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),MAX(0,1-(G10-F10)/MAX(ABS(F10),ABS(G10))))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),MAX(0,1-(F10-G10)/MAX(ABS(F10),ABS(G10))))))))</f>
         <v/>
       </c>
       <c r="I10" s="25">
@@ -2125,7 +2140,7 @@
         <v/>
       </c>
       <c r="J10" s="24">
-        <f>IF(OR(B10="",H10=""),"",IF(H10&gt;=1,"Atingido",IF(H10&gt;=I10-0.1,"No ritmo",IF(H10&gt;=I10-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B10="","",IF(H10="","Faltam dados",IF(H10&gt;=1,"Atingido",IF(H10&gt;=I10-0.1,"No ritmo",IF(H10&gt;=I10-0.25,"Atenção","Em risco")))))</f>
         <v/>
       </c>
       <c r="K10" s="36" t="n"/>
@@ -2162,7 +2177,7 @@
         <v>6</v>
       </c>
       <c r="H11" s="25">
-        <f>IF(OR(B11="",G11=""),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),IF(G11=0,0,MAX(0,F11/G11)))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),IF(F11=0,0,MAX(0,G11/F11))))))</f>
+        <f>IF(B11="","",IF(OR(NOT(ISNUMBER(E11)),NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),MAX(0,1-(G11-F11)/MAX(ABS(F11),ABS(G11))))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),MAX(0,1-(F11-G11)/MAX(ABS(F11),ABS(G11))))))))</f>
         <v>0.75</v>
       </c>
       <c r="I11" s="25">
@@ -2170,7 +2185,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J11" s="24" t="str">
-        <f>IF(OR(B11="",H11=""),"",IF(H11&gt;=1,"Atingido",IF(H11&gt;=I11-0.1,"No ritmo",IF(H11&gt;=I11-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B11="","",IF(H11="","Faltam dados",IF(H11&gt;=1,"Atingido",IF(H11&gt;=I11-0.1,"No ritmo",IF(H11&gt;=I11-0.25,"Atenção","Em risco")))))</f>
         <v>No ritmo</v>
       </c>
       <c r="K11" s="36" t="inlineStr">
@@ -2211,7 +2226,7 @@
         <v>53000</v>
       </c>
       <c r="H12" s="25">
-        <f>IF(OR(B12="",G12=""),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),IF(G12=0,0,MAX(0,F12/G12)))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),IF(F12=0,0,MAX(0,G12/F12))))))</f>
+        <f>IF(B12="","",IF(OR(NOT(ISNUMBER(E12)),NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),MAX(0,1-(G12-F12)/MAX(ABS(F12),ABS(G12))))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),MAX(0,1-(F12-G12)/MAX(ABS(F12),ABS(G12))))))))</f>
         <v>0.883333333333333</v>
       </c>
       <c r="I12" s="25">
@@ -2219,7 +2234,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J12" s="24" t="str">
-        <f>IF(OR(B12="",H12=""),"",IF(H12&gt;=1,"Atingido",IF(H12&gt;=I12-0.1,"No ritmo",IF(H12&gt;=I12-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B12="","",IF(H12="","Faltam dados",IF(H12&gt;=1,"Atingido",IF(H12&gt;=I12-0.1,"No ritmo",IF(H12&gt;=I12-0.25,"Atenção","Em risco")))))</f>
         <v>No ritmo</v>
       </c>
       <c r="K12" s="36" t="inlineStr">
@@ -2260,7 +2275,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="25">
-        <f>IF(OR(B13="",G13=""),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),IF(G13=0,0,MAX(0,F13/G13)))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),IF(F13=0,0,MAX(0,G13/F13))))))</f>
+        <f>IF(B13="","",IF(OR(NOT(ISNUMBER(E13)),NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),MAX(0,1-(G13-F13)/MAX(ABS(F13),ABS(G13))))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),MAX(0,1-(F13-G13)/MAX(ABS(F13),ABS(G13))))))))</f>
         <v>0.5</v>
       </c>
       <c r="I13" s="25">
@@ -2268,7 +2283,7 @@
         <v>0.824175824175824</v>
       </c>
       <c r="J13" s="24" t="str">
-        <f>IF(OR(B13="",H13=""),"",IF(H13&gt;=1,"Atingido",IF(H13&gt;=I13-0.1,"No ritmo",IF(H13&gt;=I13-0.25,"Atenção","Em risco"))))</f>
+        <f>IF(B13="","",IF(H13="","Faltam dados",IF(H13&gt;=1,"Atingido",IF(H13&gt;=I13-0.1,"No ritmo",IF(H13&gt;=I13-0.25,"Atenção","Em risco")))))</f>
         <v>Em risco</v>
       </c>
       <c r="K13" s="36" t="inlineStr">
@@ -2285,7 +2300,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Progresso: valor atual no alvo = 100 %; fora do alvo, é o caminho andado entre o ponto de partida e a meta — e, quando o ponto de partida já estava dentro da meta (um teto ou piso a manter), é meta ÷ atual (16 pacientes para um teto de 8 = 50 %). Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso). A planilha avisa; a ação é do escritório.</t>
+          <t>Progresso: só é calculado com ponto de partida, meta e valor atual preenchidos (zero vale; vazio vira "Faltam dados" e fica fora das contagens). Valor atual no alvo = 100 %. Fora do alvo, é o caminho andado entre o ponto de partida e a meta; quando o ponto de partida já estava dentro da meta (um limite a manter), é a distância ao limite: para um teto ("Menor é melhor"), meta ÷ atual (16 para um teto de 8 = 50 %); para um piso ("Maior é melhor"), atual ÷ meta (4 para um piso de 8 = 50 %). Com zero ou valores negativos (um limite de prejuízo, por exemplo) a conta usa o maior valor absoluto como escala e nunca dá 100 % sem o alvo estar cumprido. Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso). A planilha avisa; a ação é do escritório.</t>
         </is>
       </c>
     </row>
@@ -2308,15 +2323,18 @@
   </mergeCells>
   <conditionalFormatting sqref="J5:J13">
     <cfRule type="expression" priority="1" dxfId="0">
+      <formula>J5="Faltam dados"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>J5="Atingido"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>J5="No ritmo"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="4" dxfId="3">
       <formula>J5="Atenção"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="5" dxfId="4">
       <formula>J5="Em risco"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2847,7 +2865,7 @@
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:O4">
-    <cfRule type="expression" priority="1" dxfId="4">
+    <cfRule type="expression" priority="1" dxfId="5">
       <formula>COLUMN()-2=INDIRECT("Config!$B$9")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
-        <f>IFERROR(AVERAGEIFS(Metas!$H$5:$H$13,Metas!$B$5:$B$13,"&lt;&gt;"),0)</f>
+        <f>IF(COUNT(Metas!$H$5:$H$13)=0,"Faltam dados",AVERAGEIFS(Metas!$H$5:$H$13,Metas!$B$5:$B$13,"&lt;&gt;"))</f>
         <v>0.601505376344086</v>
       </c>
       <c r="H5" s="14" t="n"/>
@@ -1111,7 +1111,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="25">
-        <f>IF(OR(Metas!$A$5="",B9=0),"",AVERAGEIFS(Metas!$H$5:$H$7,Metas!$B$5:$B$7,"&lt;&gt;"))</f>
+        <f>IF(OR(Metas!$A$5="",B9=0),"",IF(COUNT(Metas!$H$5:$H$7)=0,"Faltam dados",AVERAGEIFS(Metas!$H$5:$H$7,Metas!$B$5:$B$7,"&lt;&gt;")))</f>
         <v>0.368333333333333</v>
       </c>
       <c r="D9" s="24">
@@ -1123,7 +1123,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="26" t="str">
-        <f>IF(C9="","",REPT("█",ROUND(C9*30,0)))</f>
+        <f>IF(ISNUMBER(C9),REPT("█",ROUND(C9*30,0)),"")</f>
         <v>███████████</v>
       </c>
       <c r="G9" s="21" t="n"/>
@@ -1139,7 +1139,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="25">
-        <f>IF(OR(Metas!$A$8="",B10=0),"",AVERAGEIFS(Metas!$H$8:$H$10,Metas!$B$8:$B$10,"&lt;&gt;"))</f>
+        <f>IF(OR(Metas!$A$8="",B10=0),"",IF(COUNT(Metas!$H$8:$H$10)=0,"Faltam dados",AVERAGEIFS(Metas!$H$8:$H$10,Metas!$B$8:$B$10,"&lt;&gt;")))</f>
         <v>0.786854838709677</v>
       </c>
       <c r="D10" s="24">
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="26" t="str">
-        <f>IF(C10="","",REPT("█",ROUND(C10*30,0)))</f>
+        <f>IF(ISNUMBER(C10),REPT("█",ROUND(C10*30,0)),"")</f>
         <v>████████████████████████</v>
       </c>
       <c r="G10" s="21" t="n"/>
@@ -1167,7 +1167,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="25">
-        <f>IF(OR(Metas!$A$11="",B11=0),"",AVERAGEIFS(Metas!$H$11:$H$13,Metas!$B$11:$B$13,"&lt;&gt;"))</f>
+        <f>IF(OR(Metas!$A$11="",B11=0),"",IF(COUNT(Metas!$H$11:$H$13)=0,"Faltam dados",AVERAGEIFS(Metas!$H$11:$H$13,Metas!$B$11:$B$13,"&lt;&gt;")))</f>
         <v>0.711111111111111</v>
       </c>
       <c r="D11" s="24">
@@ -1179,7 +1179,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="26" t="str">
-        <f>IF(C11="","",REPT("█",ROUND(C11*30,0)))</f>
+        <f>IF(ISNUMBER(C11),REPT("█",ROUND(C11*30,0)),"")</f>
         <v>█████████████████████</v>
       </c>
       <c r="G11" s="21" t="n"/>
@@ -1901,7 +1901,7 @@
         <v>4.6</v>
       </c>
       <c r="H5" s="25">
-        <f>IF(B5="","",IF(OR(NOT(ISNUMBER(E5)),NOT(ISNUMBER(F5)),NOT(ISNUMBER(G5))),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),MAX(0,1-(G5-F5)/MAX(ABS(F5),ABS(G5))))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),MAX(0,1-(F5-G5)/MAX(ABS(F5),ABS(G5))))))))</f>
+        <f>IF(B5="","",IF(OR(NOT(ISNUMBER(E5)),NOT(ISNUMBER(F5)),NOT(ISNUMBER(G5)),AND(K5&lt;&gt;"Menor é melhor",K5&lt;&gt;"Maior é melhor")),"",IF(K5="Menor é melhor",IF(G5&lt;=F5,1,IF(E5&gt;F5,MAX(0,(E5-G5)/(E5-F5)),MAX(0,1-(G5-F5)/MAX(ABS(F5),ABS(G5))))),IF(G5&gt;=F5,1,IF(E5&lt;F5,MAX(0,(G5-E5)/(F5-E5)),MAX(0,1-(F5-G5)/MAX(ABS(F5),ABS(G5))))))))</f>
         <v>0</v>
       </c>
       <c r="I5" s="25">
@@ -1950,7 +1950,7 @@
         <v>12000</v>
       </c>
       <c r="H6" s="25">
-        <f>IF(B6="","",IF(OR(NOT(ISNUMBER(E6)),NOT(ISNUMBER(F6)),NOT(ISNUMBER(G6))),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),MAX(0,1-(G6-F6)/MAX(ABS(F6),ABS(G6))))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),MAX(0,1-(F6-G6)/MAX(ABS(F6),ABS(G6))))))))</f>
+        <f>IF(B6="","",IF(OR(NOT(ISNUMBER(E6)),NOT(ISNUMBER(F6)),NOT(ISNUMBER(G6)),AND(K6&lt;&gt;"Menor é melhor",K6&lt;&gt;"Maior é melhor")),"",IF(K6="Menor é melhor",IF(G6&lt;=F6,1,IF(E6&gt;F6,MAX(0,(E6-G6)/(E6-F6)),MAX(0,1-(G6-F6)/MAX(ABS(F6),ABS(G6))))),IF(G6&gt;=F6,1,IF(E6&lt;F6,MAX(0,(G6-E6)/(F6-E6)),MAX(0,1-(F6-G6)/MAX(ABS(F6),ABS(G6))))))))</f>
         <v>0.48</v>
       </c>
       <c r="I6" s="25">
@@ -1999,7 +1999,7 @@
         <v>9400</v>
       </c>
       <c r="H7" s="25">
-        <f>IF(B7="","",IF(OR(NOT(ISNUMBER(E7)),NOT(ISNUMBER(F7)),NOT(ISNUMBER(G7))),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),MAX(0,1-(G7-F7)/MAX(ABS(F7),ABS(G7))))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),MAX(0,1-(F7-G7)/MAX(ABS(F7),ABS(G7))))))))</f>
+        <f>IF(B7="","",IF(OR(NOT(ISNUMBER(E7)),NOT(ISNUMBER(F7)),NOT(ISNUMBER(G7)),AND(K7&lt;&gt;"Menor é melhor",K7&lt;&gt;"Maior é melhor")),"",IF(K7="Menor é melhor",IF(G7&lt;=F7,1,IF(E7&gt;F7,MAX(0,(E7-G7)/(E7-F7)),MAX(0,1-(G7-F7)/MAX(ABS(F7),ABS(G7))))),IF(G7&gt;=F7,1,IF(E7&lt;F7,MAX(0,(G7-E7)/(F7-E7)),MAX(0,1-(F7-G7)/MAX(ABS(F7),ABS(G7))))))))</f>
         <v>0.625</v>
       </c>
       <c r="I7" s="25">
@@ -2052,7 +2052,7 @@
         <v>79.5</v>
       </c>
       <c r="H8" s="25">
-        <f>IF(B8="","",IF(OR(NOT(ISNUMBER(E8)),NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),MAX(0,1-(G8-F8)/MAX(ABS(F8),ABS(G8))))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),MAX(0,1-(F8-G8)/MAX(ABS(F8),ABS(G8))))))))</f>
+        <f>IF(B8="","",IF(OR(NOT(ISNUMBER(E8)),NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8)),AND(K8&lt;&gt;"Menor é melhor",K8&lt;&gt;"Maior é melhor")),"",IF(K8="Menor é melhor",IF(G8&lt;=F8,1,IF(E8&gt;F8,MAX(0,(E8-G8)/(E8-F8)),MAX(0,1-(G8-F8)/MAX(ABS(F8),ABS(G8))))),IF(G8&gt;=F8,1,IF(E8&lt;F8,MAX(0,(G8-E8)/(F8-E8)),MAX(0,1-(F8-G8)/MAX(ABS(F8),ABS(G8))))))))</f>
         <v>0.838709677419355</v>
       </c>
       <c r="I8" s="25">
@@ -2101,7 +2101,7 @@
         <v>514.5</v>
       </c>
       <c r="H9" s="25">
-        <f>IF(B9="","",IF(OR(NOT(ISNUMBER(E9)),NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),MAX(0,1-(G9-F9)/MAX(ABS(F9),ABS(G9))))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),MAX(0,1-(F9-G9)/MAX(ABS(F9),ABS(G9))))))))</f>
+        <f>IF(B9="","",IF(OR(NOT(ISNUMBER(E9)),NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9)),AND(K9&lt;&gt;"Menor é melhor",K9&lt;&gt;"Maior é melhor")),"",IF(K9="Menor é melhor",IF(G9&lt;=F9,1,IF(E9&gt;F9,MAX(0,(E9-G9)/(E9-F9)),MAX(0,1-(G9-F9)/MAX(ABS(F9),ABS(G9))))),IF(G9&gt;=F9,1,IF(E9&lt;F9,MAX(0,(G9-E9)/(F9-E9)),MAX(0,1-(F9-G9)/MAX(ABS(F9),ABS(G9))))))))</f>
         <v>0.735</v>
       </c>
       <c r="I9" s="25">
@@ -2132,7 +2132,7 @@
       <c r="F10" s="36" t="n"/>
       <c r="G10" s="36" t="n"/>
       <c r="H10" s="25">
-        <f>IF(B10="","",IF(OR(NOT(ISNUMBER(E10)),NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),MAX(0,1-(G10-F10)/MAX(ABS(F10),ABS(G10))))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),MAX(0,1-(F10-G10)/MAX(ABS(F10),ABS(G10))))))))</f>
+        <f>IF(B10="","",IF(OR(NOT(ISNUMBER(E10)),NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10)),AND(K10&lt;&gt;"Menor é melhor",K10&lt;&gt;"Maior é melhor")),"",IF(K10="Menor é melhor",IF(G10&lt;=F10,1,IF(E10&gt;F10,MAX(0,(E10-G10)/(E10-F10)),MAX(0,1-(G10-F10)/MAX(ABS(F10),ABS(G10))))),IF(G10&gt;=F10,1,IF(E10&lt;F10,MAX(0,(G10-E10)/(F10-E10)),MAX(0,1-(F10-G10)/MAX(ABS(F10),ABS(G10))))))))</f>
         <v/>
       </c>
       <c r="I10" s="25">
@@ -2177,7 +2177,7 @@
         <v>6</v>
       </c>
       <c r="H11" s="25">
-        <f>IF(B11="","",IF(OR(NOT(ISNUMBER(E11)),NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),MAX(0,1-(G11-F11)/MAX(ABS(F11),ABS(G11))))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),MAX(0,1-(F11-G11)/MAX(ABS(F11),ABS(G11))))))))</f>
+        <f>IF(B11="","",IF(OR(NOT(ISNUMBER(E11)),NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11)),AND(K11&lt;&gt;"Menor é melhor",K11&lt;&gt;"Maior é melhor")),"",IF(K11="Menor é melhor",IF(G11&lt;=F11,1,IF(E11&gt;F11,MAX(0,(E11-G11)/(E11-F11)),MAX(0,1-(G11-F11)/MAX(ABS(F11),ABS(G11))))),IF(G11&gt;=F11,1,IF(E11&lt;F11,MAX(0,(G11-E11)/(F11-E11)),MAX(0,1-(F11-G11)/MAX(ABS(F11),ABS(G11))))))))</f>
         <v>0.75</v>
       </c>
       <c r="I11" s="25">
@@ -2226,7 +2226,7 @@
         <v>53000</v>
       </c>
       <c r="H12" s="25">
-        <f>IF(B12="","",IF(OR(NOT(ISNUMBER(E12)),NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),MAX(0,1-(G12-F12)/MAX(ABS(F12),ABS(G12))))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),MAX(0,1-(F12-G12)/MAX(ABS(F12),ABS(G12))))))))</f>
+        <f>IF(B12="","",IF(OR(NOT(ISNUMBER(E12)),NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12)),AND(K12&lt;&gt;"Menor é melhor",K12&lt;&gt;"Maior é melhor")),"",IF(K12="Menor é melhor",IF(G12&lt;=F12,1,IF(E12&gt;F12,MAX(0,(E12-G12)/(E12-F12)),MAX(0,1-(G12-F12)/MAX(ABS(F12),ABS(G12))))),IF(G12&gt;=F12,1,IF(E12&lt;F12,MAX(0,(G12-E12)/(F12-E12)),MAX(0,1-(F12-G12)/MAX(ABS(F12),ABS(G12))))))))</f>
         <v>0.883333333333333</v>
       </c>
       <c r="I12" s="25">
@@ -2275,7 +2275,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="25">
-        <f>IF(B13="","",IF(OR(NOT(ISNUMBER(E13)),NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),MAX(0,1-(G13-F13)/MAX(ABS(F13),ABS(G13))))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),MAX(0,1-(F13-G13)/MAX(ABS(F13),ABS(G13))))))))</f>
+        <f>IF(B13="","",IF(OR(NOT(ISNUMBER(E13)),NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13)),AND(K13&lt;&gt;"Menor é melhor",K13&lt;&gt;"Maior é melhor")),"",IF(K13="Menor é melhor",IF(G13&lt;=F13,1,IF(E13&gt;F13,MAX(0,(E13-G13)/(E13-F13)),MAX(0,1-(G13-F13)/MAX(ABS(F13),ABS(G13))))),IF(G13&gt;=F13,1,IF(E13&lt;F13,MAX(0,(G13-E13)/(F13-E13)),MAX(0,1-(F13-G13)/MAX(ABS(F13),ABS(G13))))))))</f>
         <v>0.5</v>
       </c>
       <c r="I13" s="25">
@@ -2300,7 +2300,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Progresso: só é calculado com ponto de partida, meta e valor atual preenchidos (zero vale; vazio vira "Faltam dados" e fica fora das contagens). Valor atual no alvo = 100 %. Fora do alvo, é o caminho andado entre o ponto de partida e a meta; quando o ponto de partida já estava dentro da meta (um limite a manter), é a distância ao limite: para um teto ("Menor é melhor"), meta ÷ atual (16 para um teto de 8 = 50 %); para um piso ("Maior é melhor"), atual ÷ meta (4 para um piso de 8 = 50 %). Com zero ou valores negativos (um limite de prejuízo, por exemplo) a conta usa o maior valor absoluto como escala e nunca dá 100 % sem o alvo estar cumprido. Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso). A planilha avisa; a ação é do escritório.</t>
+          <t>Progresso: só é calculado com ponto de partida, meta, valor atual e sentido preenchidos (zero vale; vazio vira "Faltam dados" e fica fora das contagens; sem nenhuma medição, a média do Painel também diz "Faltam dados"). Valor atual no alvo = 100 %. Fora do alvo, é o caminho andado entre o ponto de partida e a meta; quando o ponto de partida já estava dentro da meta (um limite a manter), é a distância ao limite: para um teto ("Menor é melhor"), meta ÷ atual (16 para um teto de 8 = 50 %); para um piso ("Maior é melhor"), atual ÷ meta (4 para um piso de 8 = 50 %). Com zero ou valores negativos (um limite de prejuízo, por exemplo) a conta usa o maior valor absoluto como escala e nunca dá 100 % sem o alvo estar cumprido. Semáforo: Atingido (100%); No ritmo (progresso até 10 pontos abaixo do tempo decorrido); Atenção (até 25 pontos abaixo); Em risco (mais que isso). A planilha avisa; a ação é do escritório.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
@@ -1244,11 +1244,11 @@
         <v>Rafael Lima</v>
       </c>
       <c r="C15" s="28">
-        <f>IF(Metas!B5="","",Metas!G5)</f>
+        <f>IF(OR(Metas!B5="",NOT(ISNUMBER(Metas!G5))),"",Metas!G5)</f>
         <v>4.6</v>
       </c>
       <c r="D15" s="28">
-        <f>IF(Metas!B5="","",Metas!F5)</f>
+        <f>IF(OR(Metas!B5="",NOT(ISNUMBER(Metas!F5))),"",Metas!F5)</f>
         <v>3</v>
       </c>
       <c r="E15" s="25">
@@ -1278,11 +1278,11 @@
         <v>Marina Ferraz</v>
       </c>
       <c r="C16" s="28">
-        <f>IF(Metas!B6="","",Metas!G6)</f>
+        <f>IF(OR(Metas!B6="",NOT(ISNUMBER(Metas!G6))),"",Metas!G6)</f>
         <v>12000</v>
       </c>
       <c r="D16" s="28">
-        <f>IF(Metas!B6="","",Metas!F6)</f>
+        <f>IF(OR(Metas!B6="",NOT(ISNUMBER(Metas!F6))),"",Metas!F6)</f>
         <v>18500</v>
       </c>
       <c r="E16" s="25">
@@ -1312,11 +1312,11 @@
         <v>Marina Ferraz</v>
       </c>
       <c r="C17" s="28">
-        <f>IF(Metas!B7="","",Metas!G7)</f>
+        <f>IF(OR(Metas!B7="",NOT(ISNUMBER(Metas!G7))),"",Metas!G7)</f>
         <v>9400</v>
       </c>
       <c r="D17" s="28">
-        <f>IF(Metas!B7="","",Metas!F7)</f>
+        <f>IF(OR(Metas!B7="",NOT(ISNUMBER(Metas!F7))),"",Metas!F7)</f>
         <v>11320</v>
       </c>
       <c r="E17" s="25">
@@ -1346,11 +1346,11 @@
         <v>Rafael Lima</v>
       </c>
       <c r="C18" s="28">
-        <f>IF(Metas!B8="","",Metas!G8)</f>
+        <f>IF(OR(Metas!B8="",NOT(ISNUMBER(Metas!G8))),"",Metas!G8)</f>
         <v>79.5</v>
       </c>
       <c r="D18" s="28">
-        <f>IF(Metas!B8="","",Metas!F8)</f>
+        <f>IF(OR(Metas!B8="",NOT(ISNUMBER(Metas!F8))),"",Metas!F8)</f>
         <v>80</v>
       </c>
       <c r="E18" s="25">
@@ -1380,11 +1380,11 @@
         <v>Marina Ferraz</v>
       </c>
       <c r="C19" s="28">
-        <f>IF(Metas!B9="","",Metas!G9)</f>
+        <f>IF(OR(Metas!B9="",NOT(ISNUMBER(Metas!G9))),"",Metas!G9)</f>
         <v>514.5</v>
       </c>
       <c r="D19" s="28">
-        <f>IF(Metas!B9="","",Metas!F9)</f>
+        <f>IF(OR(Metas!B9="",NOT(ISNUMBER(Metas!F9))),"",Metas!F9)</f>
         <v>700</v>
       </c>
       <c r="E19" s="25">
@@ -1414,11 +1414,11 @@
         <v/>
       </c>
       <c r="C20" s="28">
-        <f>IF(Metas!B10="","",Metas!G10)</f>
+        <f>IF(OR(Metas!B10="",NOT(ISNUMBER(Metas!G10))),"",Metas!G10)</f>
         <v/>
       </c>
       <c r="D20" s="28">
-        <f>IF(Metas!B10="","",Metas!F10)</f>
+        <f>IF(OR(Metas!B10="",NOT(ISNUMBER(Metas!F10))),"",Metas!F10)</f>
         <v/>
       </c>
       <c r="E20" s="25">
@@ -1448,11 +1448,11 @@
         <v>Marina Ferraz</v>
       </c>
       <c r="C21" s="28">
-        <f>IF(Metas!B11="","",Metas!G11)</f>
+        <f>IF(OR(Metas!B11="",NOT(ISNUMBER(Metas!G11))),"",Metas!G11)</f>
         <v>6</v>
       </c>
       <c r="D21" s="28">
-        <f>IF(Metas!B11="","",Metas!F11)</f>
+        <f>IF(OR(Metas!B11="",NOT(ISNUMBER(Metas!F11))),"",Metas!F11)</f>
         <v>8</v>
       </c>
       <c r="E21" s="25">
@@ -1482,11 +1482,11 @@
         <v>Marina Ferraz</v>
       </c>
       <c r="C22" s="28">
-        <f>IF(Metas!B12="","",Metas!G12)</f>
+        <f>IF(OR(Metas!B12="",NOT(ISNUMBER(Metas!G12))),"",Metas!G12)</f>
         <v>53000</v>
       </c>
       <c r="D22" s="28">
-        <f>IF(Metas!B12="","",Metas!F12)</f>
+        <f>IF(OR(Metas!B12="",NOT(ISNUMBER(Metas!F12))),"",Metas!F12)</f>
         <v>60000</v>
       </c>
       <c r="E22" s="25">
@@ -1516,11 +1516,11 @@
         <v>Rafael Lima</v>
       </c>
       <c r="C23" s="28">
-        <f>IF(Metas!B13="","",Metas!G13)</f>
+        <f>IF(OR(Metas!B13="",NOT(ISNUMBER(Metas!G13))),"",Metas!G13)</f>
         <v>1</v>
       </c>
       <c r="D23" s="28">
-        <f>IF(Metas!B13="","",Metas!F13)</f>
+        <f>IF(OR(Metas!B13="",NOT(ISNUMBER(Metas!F13))),"",Metas!F13)</f>
         <v>0</v>
       </c>
       <c r="E23" s="25">
@@ -2474,7 +2474,7 @@
         <v>Inadimplência: vencido ÷ (pago + vencido) (%)</v>
       </c>
       <c r="B5" s="24">
-        <f>IF(Metas!B5="","",Metas!F5)</f>
+        <f>IF(OR(Metas!B5="",NOT(ISNUMBER(Metas!F5))),"",Metas!F5)</f>
         <v>3</v>
       </c>
       <c r="C5" s="36" t="n">
@@ -2519,7 +2519,7 @@
         <v>Reserva guardada em conta separada (R$)</v>
       </c>
       <c r="B6" s="24">
-        <f>IF(Metas!B6="","",Metas!F6)</f>
+        <f>IF(OR(Metas!B6="",NOT(ISNUMBER(Metas!F6))),"",Metas!F6)</f>
         <v>18500</v>
       </c>
       <c r="C6" s="36" t="n">
@@ -2564,7 +2564,7 @@
         <v>Conta de provisão de impostos, 13º e férias (R$)</v>
       </c>
       <c r="B7" s="24">
-        <f>IF(Metas!B7="","",Metas!F7)</f>
+        <f>IF(OR(Metas!B7="",NOT(ISNUMBER(Metas!F7))),"",Metas!F7)</f>
         <v>11320</v>
       </c>
       <c r="C7" s="36" t="n">
@@ -2609,7 +2609,7 @@
         <v>Horas faturáveis no mês (%)</v>
       </c>
       <c r="B8" s="24">
-        <f>IF(Metas!B8="","",Metas!F8)</f>
+        <f>IF(OR(Metas!B8="",NOT(ISNUMBER(Metas!F8))),"",Metas!F8)</f>
         <v>80</v>
       </c>
       <c r="C8" s="36" t="n">
@@ -2654,7 +2654,7 @@
         <v>Horas faturáveis lançadas no trimestre (h)</v>
       </c>
       <c r="B9" s="24">
-        <f>IF(Metas!B9="","",Metas!F9)</f>
+        <f>IF(OR(Metas!B9="",NOT(ISNUMBER(Metas!F9))),"",Metas!F9)</f>
         <v>700</v>
       </c>
       <c r="C9" s="36" t="n">
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="B10" s="24">
-        <f>IF(Metas!B10="","",Metas!F10)</f>
+        <f>IF(OR(Metas!B10="",NOT(ISNUMBER(Metas!F10))),"",Metas!F10)</f>
         <v/>
       </c>
       <c r="C10" s="36" t="n"/>
@@ -2722,7 +2722,7 @@
         <v>Propostas fechadas no trimestre</v>
       </c>
       <c r="B11" s="24">
-        <f>IF(Metas!B11="","",Metas!F11)</f>
+        <f>IF(OR(Metas!B11="",NOT(ISNUMBER(Metas!F11))),"",Metas!F11)</f>
         <v>8</v>
       </c>
       <c r="C11" s="36" t="n">
@@ -2767,7 +2767,7 @@
         <v>Honorários fechados no trimestre (R$)</v>
       </c>
       <c r="B12" s="24">
-        <f>IF(Metas!B12="","",Metas!F12)</f>
+        <f>IF(OR(Metas!B12="",NOT(ISNUMBER(Metas!F12))),"",Metas!F12)</f>
         <v>60000</v>
       </c>
       <c r="C12" s="36" t="n">
@@ -2812,7 +2812,7 @@
         <v>Propostas paradas há mais de 14 dias</v>
       </c>
       <c r="B13" s="24">
-        <f>IF(Metas!B13="","",Metas!F13)</f>
+        <f>IF(OR(Metas!B13="",NOT(ISNUMBER(Metas!F13))),"",Metas!F13)</f>
         <v>0</v>
       </c>
       <c r="C13" s="36" t="n">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
@@ -1240,7 +1240,7 @@
         <v>Inadimplência: vencido ÷ (pago + vencido) (%)</v>
       </c>
       <c r="B15" s="24" t="str">
-        <f>IF(Metas!B5="","",Metas!C5)</f>
+        <f>IF(OR(Metas!B5="",Metas!C5=""),"",Metas!C5)</f>
         <v>Rafael Lima</v>
       </c>
       <c r="C15" s="28">
@@ -1274,7 +1274,7 @@
         <v>Reserva guardada em conta separada (R$)</v>
       </c>
       <c r="B16" s="24" t="str">
-        <f>IF(Metas!B6="","",Metas!C6)</f>
+        <f>IF(OR(Metas!B6="",Metas!C6=""),"",Metas!C6)</f>
         <v>Marina Ferraz</v>
       </c>
       <c r="C16" s="28">
@@ -1308,7 +1308,7 @@
         <v>Conta de provisão de impostos, 13º e férias (R$)</v>
       </c>
       <c r="B17" s="24" t="str">
-        <f>IF(Metas!B7="","",Metas!C7)</f>
+        <f>IF(OR(Metas!B7="",Metas!C7=""),"",Metas!C7)</f>
         <v>Marina Ferraz</v>
       </c>
       <c r="C17" s="28">
@@ -1342,7 +1342,7 @@
         <v>Horas faturáveis no mês (%)</v>
       </c>
       <c r="B18" s="24" t="str">
-        <f>IF(Metas!B8="","",Metas!C8)</f>
+        <f>IF(OR(Metas!B8="",Metas!C8=""),"",Metas!C8)</f>
         <v>Rafael Lima</v>
       </c>
       <c r="C18" s="28">
@@ -1376,7 +1376,7 @@
         <v>Horas faturáveis lançadas no trimestre (h)</v>
       </c>
       <c r="B19" s="24" t="str">
-        <f>IF(Metas!B9="","",Metas!C9)</f>
+        <f>IF(OR(Metas!B9="",Metas!C9=""),"",Metas!C9)</f>
         <v>Marina Ferraz</v>
       </c>
       <c r="C19" s="28">
@@ -1410,7 +1410,7 @@
         <v/>
       </c>
       <c r="B20" s="24">
-        <f>IF(Metas!B10="","",Metas!C10)</f>
+        <f>IF(OR(Metas!B10="",Metas!C10=""),"",Metas!C10)</f>
         <v/>
       </c>
       <c r="C20" s="28">
@@ -1444,7 +1444,7 @@
         <v>Propostas fechadas no trimestre</v>
       </c>
       <c r="B21" s="24" t="str">
-        <f>IF(Metas!B11="","",Metas!C11)</f>
+        <f>IF(OR(Metas!B11="",Metas!C11=""),"",Metas!C11)</f>
         <v>Marina Ferraz</v>
       </c>
       <c r="C21" s="28">
@@ -1478,7 +1478,7 @@
         <v>Honorários fechados no trimestre (R$)</v>
       </c>
       <c r="B22" s="24" t="str">
-        <f>IF(Metas!B12="","",Metas!C12)</f>
+        <f>IF(OR(Metas!B12="",Metas!C12=""),"",Metas!C12)</f>
         <v>Marina Ferraz</v>
       </c>
       <c r="C22" s="28">
@@ -1512,7 +1512,7 @@
         <v>Propostas paradas há mais de 14 dias</v>
       </c>
       <c r="B23" s="24" t="str">
-        <f>IF(Metas!B13="","",Metas!C13)</f>
+        <f>IF(OR(Metas!B13="",Metas!C13=""),"",Metas!C13)</f>
         <v>Rafael Lima</v>
       </c>
       <c r="C23" s="28">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/19-metas-do-trimestre.xlsx
@@ -819,6 +819,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -935,7 +936,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e semáforos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
